--- a/GATEWAY/A1#111#CODEBYTESRLXX/CODEBYTESRL/codebyte.medisolution/2026.03/accreditamento-checklist_V9.0.0.xlsx
+++ b/GATEWAY/A1#111#CODEBYTESRLXX/CODEBYTESRL/codebyte.medisolution/2026.03/accreditamento-checklist_V9.0.0.xlsx
@@ -3472,7 +3472,7 @@
         <v>55</v>
       </c>
       <c r="R10" t="s" s="55">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S10" t="s" s="55">
         <v>56</v>
@@ -3533,7 +3533,7 @@
         <v>55</v>
       </c>
       <c r="R11" t="s" s="55">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S11" t="s" s="55">
         <v>56</v>
@@ -3586,7 +3586,7 @@
         <v>55</v>
       </c>
       <c r="R12" t="s" s="55">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S12" t="s" s="55">
         <v>56</v>
@@ -3649,7 +3649,7 @@
         <v>55</v>
       </c>
       <c r="R13" t="s" s="55">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S13" t="s" s="55">
         <v>56</v>
@@ -3792,7 +3792,7 @@
         <v>55</v>
       </c>
       <c r="R16" t="s" s="55">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S16" t="s" s="55">
         <v>56</v>
@@ -3894,7 +3894,7 @@
         <v>55</v>
       </c>
       <c r="R18" t="s" s="55">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S18" t="s" s="55">
         <v>56</v>
@@ -4037,7 +4037,7 @@
         <v>55</v>
       </c>
       <c r="R21" t="s" s="55">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S21" t="s" s="55">
         <v>56</v>
@@ -4344,7 +4344,7 @@
         <v>55</v>
       </c>
       <c r="R28" t="s" s="55">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S28" t="s" s="55">
         <v>56</v>
@@ -4405,7 +4405,7 @@
         <v>55</v>
       </c>
       <c r="R29" t="s" s="55">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S29" t="s" s="55">
         <v>56</v>
